--- a/files/港岛-湾仔-活道1号.xlsx
+++ b/files/港岛-湾仔-活道1号.xlsx
@@ -635,7 +635,7 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
@@ -731,7 +731,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
@@ -777,7 +777,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
@@ -823,7 +823,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -869,7 +869,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -915,7 +915,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -961,7 +961,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-14</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-14</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2019,7 +2019,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2065,7 +2065,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-16</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2111,7 +2111,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2203,7 +2203,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-24</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -2387,7 +2387,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-24</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -2433,7 +2433,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -2571,7 +2571,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -2754,7 +2754,7 @@
           <t>A | 940呎 (3房)
 $2800万
 $29,786/呎
-(已售)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
@@ -2762,7 +2762,7 @@
           <t>B | 949呎 (3房)
 $2550万
 $26,870/呎
-(已售)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -2777,7 +2777,7 @@
           <t>A | 461呎 (2房)
 $1100万
 $23,855/呎
-(已售)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -2785,7 +2785,7 @@
           <t>B | 461呎 (2房)
 $1060万
 $22,993/呎
-(已售)</t>
+(25年-09月)</t>
         </is>
       </c>
     </row>
@@ -2800,7 +2800,7 @@
           <t>A | 461呎 (2房)
 $1080万
 $23,416/呎
-(已售)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -2808,7 +2808,7 @@
           <t>B | 461呎 (2房)
 $1039万
 $22,534/呎
-(已售)</t>
+(25年-09月)</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
           <t>A | 461呎 (2房)
 $1058万
 $22,959/呎
-(已售)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -2831,7 +2831,7 @@
           <t>B | 461呎 (2房)
 $1018万
 $22,089/呎
-(已售)</t>
+(25年-09月)</t>
         </is>
       </c>
     </row>
@@ -2846,7 +2846,7 @@
           <t>A | 461呎 (2房)
 $1038万
 $22,508/呎
-(已售)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -2854,7 +2854,7 @@
           <t>B | 461呎 (2房)
 $998万
 $21,655/呎
-(已售)</t>
+(25年-09月)</t>
         </is>
       </c>
     </row>
@@ -2869,7 +2869,7 @@
           <t>A | 461呎 (2房)
 $1017万
 $22,067/呎
-(已售)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -2877,7 +2877,7 @@
           <t>B | 461呎 (2房)
 $979万
 $21,232/呎
-(已售)</t>
+(25年-09月)</t>
         </is>
       </c>
     </row>
@@ -2892,7 +2892,7 @@
           <t>A | 461呎 (2房)
 $997万
 $21,633/呎
-(已售)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -2900,7 +2900,7 @@
           <t>B | 461呎 (2房)
 $960万
 $20,816/呎
-(已售)</t>
+(25年-09月)</t>
         </is>
       </c>
     </row>
@@ -2915,7 +2915,7 @@
           <t>A | 461呎 (2房)
 $978万
 $21,210/呎
-(已售)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -2923,7 +2923,7 @@
           <t>B | 461呎 (2房)
 $941万
 $20,408/呎
-(已售)</t>
+(25年-09月)</t>
         </is>
       </c>
     </row>
@@ -2938,7 +2938,7 @@
           <t>A | 461呎 (2房)
 $1282万
 $27,809/呎
-(已售)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -2946,7 +2946,7 @@
           <t>B | 461呎 (2房)
 $925万
 $20,074/呎
-(已售)</t>
+(25年-09月)</t>
         </is>
       </c>
     </row>
@@ -2961,7 +2961,7 @@
           <t>A | 461呎 (2房)
 $945万
 $20,503/呎
-(已售)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -2969,7 +2969,7 @@
           <t>B | 461呎 (2房)
 $910万
 $19,740/呎
-(已售)</t>
+(25年-09月)</t>
         </is>
       </c>
     </row>
@@ -2984,7 +2984,7 @@
           <t>A | 461呎 (2房)
 $1231万
 $26,707/呎
-(已售)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -2992,7 +2992,7 @@
           <t>B | 461呎 (2房)
 $901万
 $19,553/呎
-(已售)</t>
+(25年-09月)</t>
         </is>
       </c>
     </row>
@@ -3007,7 +3007,7 @@
           <t>A | 461呎 (2房)
 $966万
 $20,961/呎
-(已售)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -3015,7 +3015,7 @@
           <t>B | 461呎 (2房)
 $932万
 $20,208/呎
-(已售)</t>
+(25年-09月)</t>
         </is>
       </c>
     </row>
@@ -3030,7 +3030,7 @@
           <t>A | 461呎 (2房)
 $926万
 $20,098/呎
-(已售)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -3038,7 +3038,7 @@
           <t>B | 461呎 (2房)
 $894万
 $19,388/呎
-(已售)</t>
+(25年-09月)</t>
         </is>
       </c>
     </row>
@@ -3053,7 +3053,7 @@
           <t>A | 461呎 (2房)
 $911万
 $19,770/呎
-(已售)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -3061,7 +3061,7 @@
           <t>B | 461呎 (2房)
 $885万
 $19,206/呎
-(已售)</t>
+(25年-09月)</t>
         </is>
       </c>
     </row>
@@ -3076,7 +3076,7 @@
           <t>A | 461呎 (2房)
 $1160万
 $25,174/呎
-(已售)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -3084,7 +3084,7 @@
           <t>B | 461呎 (2房)
 $874万
 $18,952/呎
-(已售)</t>
+(25年-09月)</t>
         </is>
       </c>
     </row>
@@ -3099,7 +3099,7 @@
           <t>A | 461呎 (2房)
 $876万
 $19,000/呎
-(已售)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -3107,7 +3107,7 @@
           <t>B | 461呎 (2房)
 $1112万
 $24,132/呎
-(已售)</t>
+(25年-07月)</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
           <t>A | 461呎 (2房)
 $859万
 $18,631/呎
-(已售)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -3130,7 +3130,7 @@
           <t>B | 461呎 (2房)
 $1091万
 $23,657/呎
-(已售)</t>
+(25年-06月)</t>
         </is>
       </c>
     </row>
@@ -3145,7 +3145,7 @@
           <t>A | 461呎 (2房)
 $848万
 $18,397/呎
-(已售)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -3153,7 +3153,7 @@
           <t>B | 461呎 (2房)
 $1077万
 $23,364/呎
-(已售)</t>
+(24年-11月)</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3168,7 @@
           <t>A | 461呎 (2房)
 $837万
 $18,148/呎
-(已售)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -3176,7 +3176,7 @@
           <t>B | 461呎 (2房)
 $1063万
 $23,067/呎
-(已售)</t>
+(24年-11月)</t>
         </is>
       </c>
     </row>
@@ -3191,7 +3191,7 @@
           <t>A | 461呎 (2房)
 $868万
 $18,831/呎
-(已售)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -3199,7 +3199,7 @@
           <t>B | 461呎 (2房)
 $860万
 $18,655/呎
-(已售)</t>
+(25年-09月)</t>
         </is>
       </c>
     </row>
@@ -3222,7 +3222,7 @@
           <t>B | 1279呎 (3房)
 $2880万
 $22,516/呎
-(已售)</t>
+(26年-01月)</t>
         </is>
       </c>
     </row>

--- a/files/港岛-湾仔-活道1号.xlsx
+++ b/files/港岛-湾仔-活道1号.xlsx
@@ -199,61 +199,61 @@
   <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -636,7 +636,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/港岛-湾仔-活道1号.xlsx
+++ b/files/港岛-湾仔-活道1号.xlsx
@@ -199,61 +199,61 @@
   <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -636,7 +636,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
